--- a/engine_package/Res/MuDataEditor/天使之战_v1.0.0.0/Out/cfg_synthesis_layer.xlsx
+++ b/engine_package/Res/MuDataEditor/天使之战_v1.0.0.0/Out/cfg_synthesis_layer.xlsx
@@ -97,7 +97,7 @@
     <t>一般合成</t>
   </si>
   <si>
-    <t>装备强化、透明披风、恶魔广场通行证、坐骑合成</t>
+    <t>装备强化、透明披风、恶魔广场通行证</t>
   </si>
   <si>
     <t>1#3</t>

--- a/engine_package/Res/MuDataEditor/天使之战_v1.0.0.0/Out/cfg_synthesis_layer.xlsx
+++ b/engine_package/Res/MuDataEditor/天使之战_v1.0.0.0/Out/cfg_synthesis_layer.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="38">
   <si>
     <t>编号</t>
   </si>
@@ -158,6 +158,12 @@
   </si>
   <si>
     <t>18#34#35#19#20#21#22#23#24</t>
+  </si>
+  <si>
+    <t>战旗合成</t>
+  </si>
+  <si>
+    <t>36#37#38</t>
   </si>
 </sst>
 </file>
@@ -1342,7 +1348,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E16"/>
+  <dimension ref="A1:E17"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="2" max="2" width="23.725" customWidth="1"/>
@@ -1577,6 +1583,20 @@
       </c>
       <c r="E16" t="s">
         <v>35</v>
+      </c>
+    </row>
+    <row r="17" customFormat="1" spans="1:5">
+      <c r="A17">
+        <v>13</v>
+      </c>
+      <c r="B17" t="s">
+        <v>36</v>
+      </c>
+      <c r="C17" t="s">
+        <v>36</v>
+      </c>
+      <c r="E17" t="s">
+        <v>37</v>
       </c>
     </row>
   </sheetData>

--- a/engine_package/Res/MuDataEditor/天使之战_v1.0.0.0/Out/cfg_synthesis_layer.xlsx
+++ b/engine_package/Res/MuDataEditor/天使之战_v1.0.0.0/Out/cfg_synthesis_layer.xlsx
@@ -3,8 +3,13 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\天使之战\tszz_GMTest\engine_package\Res\MuDataEditor\天使之战_v1.0.0.0\Out\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -124,7 +129,7 @@
     <t>大天使武器、卓越大天使武器、祝福大天使武器、大天使铁锤</t>
   </si>
   <si>
-    <t>11#12#13#14</t>
+    <t>13#14</t>
   </si>
   <si>
     <t>果实合成</t>
@@ -139,7 +144,7 @@
     <t>25#26#27#28</t>
   </si>
   <si>
-    <t>精通饰品箱子</t>
+    <t>耳环宝箱</t>
   </si>
   <si>
     <t>耳环合成</t>
